--- a/core.xlsx
+++ b/core.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>201063883209</t>
+          <t>201116159948</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>0106 388 3209</t>
+          <t>0111 615 9948</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
